--- a/Kharazmi/Doc_Kharazmi/رمز و پسوورد پخش ها.xlsx
+++ b/Kharazmi/Doc_Kharazmi/رمز و پسوورد پخش ها.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NEW Dashboard\Doc_Kharazmi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NEW Dashboard\Eltiam\Kharazmi\Doc_Kharazmi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A47A8A-E3EF-4FB9-B1FF-429AC4749FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96560129-9CBE-4409-BC6B-EE33458AA393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -184,9 +187,6 @@
     <t>https://www.ferdowsdco.com/Account/LogOn?returnUrl=%2Fapp</t>
   </si>
   <si>
-    <t>http://46.209.199.135:9040/(X(1)S(phtjympbmjmopx4yrey3uoq3))/login.aspx?AspxAutoDetectCookieSupport=1</t>
-  </si>
-  <si>
     <t>1234s</t>
   </si>
   <si>
@@ -262,9 +262,6 @@
     <t>sph!@#1431</t>
   </si>
   <si>
-    <t>http://46.209.99.26:25954/webport/authentication</t>
-  </si>
-  <si>
     <t>https://nsportal.alborzdco.ir/</t>
   </si>
   <si>
@@ -305,6 +302,12 @@
   </si>
   <si>
     <t>قطع همکاری</t>
+  </si>
+  <si>
+    <t>http://sphreports.salamatpakhsh.com:25954/</t>
+  </si>
+  <si>
+    <t>http://46.209.199.135:8585/RptForm.aspx</t>
   </si>
 </sst>
 </file>
@@ -721,13 +724,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1048,25 +1051,25 @@
         <v>4</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G1" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="J1" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="K1" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="26" t="s">
+      <c r="L1" s="34" t="s">
         <v>88</v>
-      </c>
-      <c r="L1" s="34" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -1077,13 +1080,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="31"/>
       <c r="G2" s="28"/>
@@ -1103,11 +1106,11 @@
       <c r="C3" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="56" t="s">
-        <v>61</v>
+      <c r="E3" s="54" t="s">
+        <v>60</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="27"/>
@@ -1125,7 +1128,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="53" t="s">
         <v>14</v>
@@ -1140,7 +1143,7 @@
       <c r="J4" s="28"/>
       <c r="K4" s="28"/>
       <c r="L4" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1156,8 +1159,8 @@
       <c r="D5" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="56" t="s">
-        <v>54</v>
+      <c r="E5" s="54" t="s">
+        <v>53</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="27"/>
@@ -1175,13 +1178,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D6" s="33" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="28"/>
@@ -1199,13 +1202,13 @@
         <v>19</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="28"/>
@@ -1223,7 +1226,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>25</v>
@@ -1245,7 +1248,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>14</v>
@@ -1269,7 +1272,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>14</v>
@@ -1316,20 +1319,20 @@
         <v>33</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
+        <v>52</v>
+      </c>
+      <c r="G12" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
       <c r="K12" s="40"/>
     </row>
     <row r="13" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1343,7 +1346,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="47" t="s">
         <v>14</v>
@@ -1359,16 +1362,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="47" t="s">
         <v>62</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>63</v>
       </c>
       <c r="K14" s="27"/>
     </row>
@@ -1377,16 +1380,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="35" t="s">
         <v>65</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>66</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" s="28"/>
@@ -1396,7 +1399,7 @@
       <c r="K15" s="28"/>
       <c r="L15" s="28"/>
       <c r="M15" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="38" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1404,16 +1407,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="D16" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="38" t="s">
         <v>70</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>71</v>
       </c>
       <c r="K16" s="52"/>
     </row>
@@ -1458,13 +1461,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="41" t="s">
         <v>73</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>74</v>
       </c>
       <c r="E19" s="21">
         <v>123456</v>
@@ -1475,16 +1478,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="E20" s="21" t="s">
         <v>81</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>83</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
@@ -1502,27 +1505,25 @@
     <hyperlink ref="C17" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E7" r:id="rId7" display="kharazmi123@" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E16" r:id="rId9" display="Akharazmi@1402" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E2" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E6" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C4" r:id="rId15" xr:uid="{1B16054C-98A7-4AC6-9515-953E9A908CA1}"/>
-    <hyperlink ref="C6" r:id="rId16" xr:uid="{87368C1D-788C-418B-B1CF-CBE3931D003C}"/>
-    <hyperlink ref="C8" r:id="rId17" xr:uid="{486FFE99-C8C3-42B7-AB7E-059051FB04F7}"/>
-    <hyperlink ref="C12" r:id="rId18" xr:uid="{B1DC0A9B-B68E-4C4B-A07B-7676D34BA557}"/>
-    <hyperlink ref="C14" r:id="rId19" xr:uid="{18462771-94A8-496B-9092-F9A1B68F8069}"/>
-    <hyperlink ref="C15" r:id="rId20" xr:uid="{EB072215-713F-4D24-9BA2-50625C8088CA}"/>
-    <hyperlink ref="C19" r:id="rId21" xr:uid="{8E128C31-C7FD-442E-9DFE-302C06FCE507}"/>
+    <hyperlink ref="C11" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E7" r:id="rId6" display="kharazmi123@" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E15" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E16" r:id="rId8" display="Akharazmi@1402" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E2" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E6" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C4" r:id="rId14" xr:uid="{1B16054C-98A7-4AC6-9515-953E9A908CA1}"/>
+    <hyperlink ref="C8" r:id="rId15" xr:uid="{486FFE99-C8C3-42B7-AB7E-059051FB04F7}"/>
+    <hyperlink ref="C12" r:id="rId16" xr:uid="{B1DC0A9B-B68E-4C4B-A07B-7676D34BA557}"/>
+    <hyperlink ref="C14" r:id="rId17" xr:uid="{18462771-94A8-496B-9092-F9A1B68F8069}"/>
+    <hyperlink ref="C15" r:id="rId18" xr:uid="{EB072215-713F-4D24-9BA2-50625C8088CA}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{8E128C31-C7FD-442E-9DFE-302C06FCE507}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="92" orientation="landscape" r:id="rId22"/>
+  <pageSetup scale="92" orientation="landscape" r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -1540,13 +1541,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
